--- a/Configs/GameConfig/Datas/unit_level.xlsx
+++ b/Configs/GameConfig/Datas/unit_level.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4e41e182ef85432a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rf8ab3a61a611413e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -368,13 +368,13 @@
         <x:v>##</x:v>
       </x:c>
       <x:c r="B4" t="str">
-        <x:v>等级ID(主键)</x:v>
+        <x:v>等级 ID（主键），从 1 开始</x:v>
       </x:c>
       <x:c r="C4" t="str">
-        <x:v>该等级伤害倍数</x:v>
+        <x:v>该等级的伤害倍率，乘到基础攻击力上</x:v>
       </x:c>
       <x:c r="D4" t="str">
-        <x:v>该等级攻速倍数</x:v>
+        <x:v>该等级的攻速倍率，乘到基础攻速上</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
